--- a/artifacts/output/test1_output.xlsx
+++ b/artifacts/output/test1_output.xlsx
@@ -28,18 +28,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF0000"/>
-        <bgColor rgb="00FF0000"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -54,11 +48,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -424,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,7 +495,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -566,18 +558,17 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>45969</v>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="C9" t="n">
         <v>116.58</v>
       </c>
-      <c r="D9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -706,68 +697,111 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n"/>
+      <c r="A17" s="1" t="n">
+        <v>45977</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Entertainment</t>
+        </is>
+      </c>
       <c r="C17" t="n">
-        <v/>
+        <v>51.77</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n"/>
+      <c r="A18" s="1" t="n">
+        <v>45978</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
       <c r="C18" t="n">
-        <v/>
+        <v>101.05</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n"/>
+      <c r="A19" s="1" t="n">
+        <v>45979</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
       <c r="C19" t="n">
-        <v/>
+        <v>42.52</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n"/>
+      <c r="A20" s="1" t="n">
+        <v>45980</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
       <c r="C20" t="n">
-        <v/>
+        <v>107.96</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45977</v>
+        <v>45981</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Entertainment</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>51.77</v>
+        <v>22.64</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Coffee</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45978</v>
+        <v>45982</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Shopping</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>101.05</v>
+        <v>0</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Groceries</t>
+          <t>Coffee</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45979</v>
+        <v>45983</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -775,17 +809,17 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>42.52</v>
+        <v>38.45</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Cinema</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45980</v>
+        <v>45984</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -793,30 +827,30 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>107.96</v>
+        <v>115.04</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45981</v>
+        <v>45985</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>22.64</v>
+        <v>71.52</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Coffee</t>
+          <t>Dinner</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45982</v>
+        <v>45986</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -824,17 +858,17 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v/>
+        <v>111.18</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Coffee</t>
+          <t>Lunch</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45983</v>
+        <v>45987</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -842,38 +876,38 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>38.45</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Cinema</t>
-        </is>
+        <v>102.98</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45984</v>
+        <v>45988</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Entertainment</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>115.04</v>
+        <v>57.13</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45985</v>
+        <v>45989</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Entertainment</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>71.52</v>
+        <v>32.5</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -883,183 +917,70 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45986</v>
+        <v>45990</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Shopping</t>
+          <t>Food</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>111.18</v>
+        <v>99.25</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>Gift</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45987</v>
+        <v>45991</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Shopping</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>102.98</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="n">
-        <v>45988</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Entertainment</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>57.13</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Groceries</t>
+        <v>35.74</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Dinner</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
-        <v>45989</v>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Entertainment</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Dinner</t>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
-        <v>45990</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Food</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>99.25</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Gift</t>
-        </is>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Total Spending (£)</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>2023.75</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
-        <v>45991</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Shopping</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>35.74</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="n"/>
-      <c r="C36" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="n"/>
-      <c r="C37" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="n"/>
-      <c r="C38" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="n"/>
-      <c r="C39" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Total Spending (£)</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>2023.75</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Average Daily Spending (£)</t>
         </is>
       </c>
-      <c r="B43" t="n">
-        <v>72.27678571428572</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Max Spending Day(s)</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2025-11-08 00:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Max Spending Amount (£)</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>116.58</v>
+      <c r="B35" t="n">
+        <v>67.45833333333333</v>
       </c>
     </row>
   </sheetData>

--- a/artifacts/output/test1_output.xlsx
+++ b/artifacts/output/test1_output.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Output" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Output" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28,12 +28,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF0000"/>
+        <bgColor rgb="00FF0000"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -48,9 +54,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -416,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,6 +461,9 @@
       <c r="C2" t="n">
         <v>106.11</v>
       </c>
+      <c r="D2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -466,6 +477,9 @@
       <c r="C3" t="n">
         <v>43.62</v>
       </c>
+      <c r="D3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -495,7 +509,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -569,6 +583,9 @@
       <c r="C9" t="n">
         <v>116.58</v>
       </c>
+      <c r="D9" t="n">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -762,6 +779,9 @@
       <c r="C20" t="n">
         <v>107.96</v>
       </c>
+      <c r="D20" t="n">
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -791,7 +811,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -829,6 +849,9 @@
       <c r="C24" t="n">
         <v>115.04</v>
       </c>
+      <c r="D24" t="n">
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -878,6 +901,9 @@
       <c r="C27" t="n">
         <v>102.98</v>
       </c>
+      <c r="D27" t="n">
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -954,34 +980,28 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
+          <t>Total Spending (£)</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2023.75</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Total Spending (£)</t>
+          <t>Average Daily Spending (£)</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2023.75</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Average Daily Spending (£)</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>67.45833333333333</v>
-      </c>
+        <v>72.27678571428571</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="3" t="n"/>
+      <c r="B276" s="3" t="n"/>
+      <c r="C276" s="3" t="n"/>
+      <c r="D276" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artifacts/output/test1_output.xlsx
+++ b/artifacts/output/test1_output.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Output" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Output" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D276"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,9 +461,6 @@
       <c r="C2" t="n">
         <v>106.11</v>
       </c>
-      <c r="D2" t="n">
-        <v/>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -477,9 +474,6 @@
       <c r="C3" t="n">
         <v>43.62</v>
       </c>
-      <c r="D3" t="n">
-        <v/>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -509,7 +503,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -572,20 +566,18 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>45969</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="3" t="n">
         <v>116.58</v>
       </c>
-      <c r="D9" t="n">
-        <v/>
-      </c>
+      <c r="D9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -779,9 +771,6 @@
       <c r="C20" t="n">
         <v>107.96</v>
       </c>
-      <c r="D20" t="n">
-        <v/>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -849,9 +838,6 @@
       <c r="C24" t="n">
         <v>115.04</v>
       </c>
-      <c r="D24" t="n">
-        <v/>
-      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -901,9 +887,6 @@
       <c r="C27" t="n">
         <v>102.98</v>
       </c>
-      <c r="D27" t="n">
-        <v/>
-      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -980,28 +963,34 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Total Spending (£)</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>2023.75</v>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>Total Spending (£)</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>2023.75</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>Average Daily Spending (£)</t>
         </is>
       </c>
-      <c r="B34" t="n">
-        <v>72.27678571428571</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" s="3" t="n"/>
-      <c r="B276" s="3" t="n"/>
-      <c r="C276" s="3" t="n"/>
-      <c r="D276" s="3" t="n"/>
+      <c r="B35" t="n">
+        <v>69.78448275862068</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artifacts/output/test1_output.xlsx
+++ b/artifacts/output/test1_output.xlsx
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>72.28</v>
+        <v>67.45999999999999</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>

--- a/artifacts/output/test1_output.xlsx
+++ b/artifacts/output/test1_output.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,9 +461,7 @@
       <c r="C2" t="n">
         <v>106.11</v>
       </c>
-      <c r="D2" t="n">
-        <v/>
-      </c>
+      <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -477,9 +475,7 @@
       <c r="C3" t="n">
         <v>43.62</v>
       </c>
-      <c r="D3" t="n">
-        <v/>
-      </c>
+      <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -583,9 +579,7 @@
       <c r="C9" s="3" t="n">
         <v>116.58</v>
       </c>
-      <c r="D9" s="3" t="n">
-        <v/>
-      </c>
+      <c r="D9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -779,9 +773,7 @@
       <c r="C20" t="n">
         <v>107.96</v>
       </c>
-      <c r="D20" t="n">
-        <v/>
-      </c>
+      <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -849,9 +841,7 @@
       <c r="C24" t="n">
         <v>115.04</v>
       </c>
-      <c r="D24" t="n">
-        <v/>
-      </c>
+      <c r="D24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -901,9 +891,7 @@
       <c r="C27" t="n">
         <v>102.98</v>
       </c>
-      <c r="D27" t="n">
-        <v/>
-      </c>
+      <c r="D27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -977,29 +965,29 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>Total Daily Spending (£)</t>
         </is>
       </c>
-      <c r="B32" t="n">
+      <c r="B33" t="n">
         <v>2023.75</v>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>Average Daily Spending (£)</t>
         </is>
       </c>
-      <c r="E32" t="n">
+      <c r="E33" t="n">
         <v>67.45999999999999</v>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>Max Daily Spending (£)</t>
         </is>
       </c>
-      <c r="H32" t="n">
+      <c r="H33" t="n">
         <v>116.58</v>
       </c>
     </row>
